--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי שבת עמיר בניון – היכן אתה?</v>
+        <v>אלירן בוזגלו - מחרוזת והלב 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9c%d7%95%d7%9e%d7%99-%d7%a9%d7%91%d7%aa-%d7%a2%d7%9e%d7%99%d7%a8-%d7%91%d7%a0%d7%99%d7%95%d7%9f-%d7%94%d7%99%d7%9b%d7%9f-%d7%90%d7%aa%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411150&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-01</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הדואט בין שלומי שבת לבין עמיר בניון בנוי כמסע רוחני־קיומי: מצד אחד וידוי אישי, שבור ואינטימי. מצד שני זעקה גדולה שמופנית כלפי מעלה, אל האל או אל העצמי האבוד. הפתיחה ("הייתי קם עוזב הכול") נשמעת כמו הצהרת בריחה. הדובר מוכן</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,88 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי שבת עמיר בניון – היכן אתה?</v>
+        <v>אלירן בוזגלו - מחרוזת והלב 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אביחי אוחנה - נתת לי חיים</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411149&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אביחי אוחנה - נתת לי חיים</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אבי בר - מחרוזת שקטים 2026</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411148&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אבי בר - מחרוזת שקטים 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אלירן בוזגלו - מחרוזת והלב 2026</v>
+        <v>שמעון בוסקילה - עולם יפה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411150&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411160&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-01</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אלירן בוזגלו - מחרוזת והלב 2026</v>
+        <v>שמעון בוסקילה - עולם יפה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אביחי אוחנה - נתת לי חיים</v>
+        <v>קובי בוקעי - האהבה שלך</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411149&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411159&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-01</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אביחי אוחנה - נתת לי חיים</v>
+        <v>קובי בוקעי - האהבה שלך</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אבי בר - מחרוזת שקטים 2026</v>
+        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
       </c>
       <c r="B4" t="str">
         <v>2026-06-01</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411148&amp;sid=db79b057e91704f5824c4dbc912b8a71</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411158&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-01</v>
@@ -545,12 +545,278 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אבי בר - מחרוזת שקטים 2026</v>
+        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מיכל בן חיים - איזה עולם</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411157&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מיכל בן חיים - איזה עולם</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מורן מצליח - מאז שהלכת</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411156&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מורן מצליח - מאז שהלכת</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411155&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>איה - באתי לרקוד</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411154&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>איה - באתי לרקוד</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ישראל צוברי - אלוקיי</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411153&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ישראל צוברי - אלוקיי</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411152&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411151&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-06-01</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L11"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בוסקילה - עולם יפה</v>
+        <v>שמעון בוסקילה – עולם יפה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411160&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://yosmusic.com/%d7%a9%d7%9e%d7%a2%d7%95%d7%9f-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%a2%d7%95%d7%9c%d7%9d-%d7%99%d7%a4%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>"עולם יפה" של שמעון בוסקילה מצליח לחבר בין כאב קולקטיבי לבין פופ נגיש מאוד. לכאורה מדובר בשיר פשוט למדי, אבל הפשטות היא חלק מרכזי מהאפקט שלו. השיר בנוי על שני צירים מנוגדים: כאב, געגוע ושבר, ומנגד תקווה, התמדה ובחירה בחיים.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בוסקילה - עולם יפה</v>
+        <v>שמעון בוסקילה – עולם יפה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>קובי בוקעי - האהבה שלך</v>
+        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411159&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%a9%d7%a8%d7%94-%d7%90%d7%aa-%d7%9c%d7%91-%d7%9c%d7%91%d7%9f-%d7%a9%d7%9c-%d7%a9%d7%95%d7%9c%d7%99-%d7%a8%d7%a0%d7%93/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-01</v>
+        <v>2026-06-02</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>שיאה של עונת החתונות בפתח. זה הזמן לקדם ללב הפלייליסט של שירי החתונה  את "לב לבן" של שולי רנד. את היוזמה ה"מסחרית" הזו לקחה לידיה מירי מסיקה בגרסה לשיר בעיבוד אורי זך. השיר "לב לבן" של  הפך תוך חודשים ספורים</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,316 +507,12 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>קובי בוקעי - האהבה שלך</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411158&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>נהוראי אריאלי &amp; שי וינר - אתה טוב</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>מיכל בן חיים - איזה עולם</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411157&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>מיכל בן חיים - איזה עולם</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>מורן מצליח - מאז שהלכת</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411156&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>מורן מצליח - מאז שהלכת</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411155&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>מורן מצליח - חשבתי שאתה לתמיד</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>איה - באתי לרקוד</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411154&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>איה - באתי לרקוד</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>ישראל צוברי - אלוקיי</v>
-      </c>
-      <c r="B9" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411153&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
-      </c>
-      <c r="D9" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E9" t="str">
-        <v/>
-      </c>
-      <c r="F9" t="str">
-        <v/>
-      </c>
-      <c r="G9" t="str">
-        <v/>
-      </c>
-      <c r="H9" t="str">
-        <v/>
-      </c>
-      <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J9" t="str">
-        <v/>
-      </c>
-      <c r="K9" t="str">
-        <v/>
-      </c>
-      <c r="L9" t="str">
-        <v>ישראל צוברי - אלוקיי</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
-      </c>
-      <c r="B10" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411152&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
-      </c>
-      <c r="D10" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E10" t="str">
-        <v/>
-      </c>
-      <c r="F10" t="str">
-        <v/>
-      </c>
-      <c r="G10" t="str">
-        <v/>
-      </c>
-      <c r="H10" t="str">
-        <v/>
-      </c>
-      <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J10" t="str">
-        <v/>
-      </c>
-      <c r="K10" t="str">
-        <v/>
-      </c>
-      <c r="L10" t="str">
-        <v>ירין יפת &amp; אפסילון - לא נמצאת</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
-      </c>
-      <c r="B11" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411151&amp;sid=025af64e8b5ae176cc6981dfe7da5d26</v>
-      </c>
-      <c r="D11" t="str">
-        <v>2026-06-01</v>
-      </c>
-      <c r="E11" t="str">
-        <v/>
-      </c>
-      <c r="F11" t="str">
-        <v/>
-      </c>
-      <c r="G11" t="str">
-        <v/>
-      </c>
-      <c r="H11" t="str">
-        <v/>
-      </c>
-      <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J11" t="str">
-        <v/>
-      </c>
-      <c r="K11" t="str">
-        <v/>
-      </c>
-      <c r="L11" t="str">
-        <v>אנה זק - ילד שמנת - גרסת הפילאטיס</v>
+        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L20"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שמעון בוסקילה – עולם יפה</v>
+        <v>סטטיק &amp; רינת בר - אקסטרה לארג'</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-02</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a9%d7%9e%d7%a2%d7%95%d7%9f-%d7%91%d7%95%d7%a1%d7%a7%d7%99%d7%9c%d7%94-%d7%a2%d7%95%d7%9c%d7%9d-%d7%99%d7%a4%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411179&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-02</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"עולם יפה" של שמעון בוסקילה מצליח לחבר בין כאב קולקטיבי לבין פופ נגיש מאוד. לכאורה מדובר בשיר פשוט למדי, אבל הפשטות היא חלק מרכזי מהאפקט שלו. השיר בנוי על שני צירים מנוגדים: כאב, געגוע ושבר, ומנגד תקווה, התמדה ובחירה בחיים.</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שמעון בוסקילה – עולם יפה</v>
+        <v>סטטיק &amp; רינת בר - אקסטרה לארג'</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
+        <v>רועי מזוז &amp; שילה בן אברהם - הסיפור של ג'וני</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-02</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%a9%d7%a8%d7%94-%d7%90%d7%aa-%d7%9c%d7%91-%d7%9c%d7%91%d7%9f-%d7%a9%d7%9c-%d7%a9%d7%95%d7%9c%d7%99-%d7%a8%d7%a0%d7%93/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411178&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-02</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>שיאה של עונת החתונות בפתח. זה הזמן לקדם ללב הפלייליסט של שירי החתונה  את "לב לבן" של שולי רנד. את היוזמה ה"מסחרית" הזו לקחה לידיה מירי מסיקה בגרסה לשיר בעיבוד אורי זך. השיר "לב לבן" של  הפך תוך חודשים ספורים</v>
+        <v/>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,12 +507,658 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>מירי מסיקה שרה את "לב לבן" של שולי רנד</v>
+        <v>רועי מזוז &amp; שילה בן אברהם - הסיפור של ג'וני</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>עופר סופר - טוב ומטיב</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411177&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>עופר סופר - טוב ומטיב</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>משינה - כמעט וכאילו</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411176&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>משינה - כמעט וכאילו</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>מיכאל כורש - שלוש בלילה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411175&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>מיכאל כורש - שלוש בלילה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>יובל לוי מארחת את דין פרינס גבאי - פאקים</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411174&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>יובל לוי מארחת את דין פרינס גבאי - פאקים</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>יובל לוי - החיה</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411173&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>יובל לוי - החיה</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>שניאור אוראל - שערי שמים פתח</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411172&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>שניאור אוראל - שערי שמים פתח</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>מתנאל אסייג - תדר</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411171&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>מתנאל אסייג - תדר</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>ליאל אוחיון - היית גבר</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411170&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>ליאל אוחיון - היית גבר</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>ישראל ברששת - מחרוזת מהנשמה 2026</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411169&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>ישראל ברששת - מחרוזת מהנשמה 2026</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>ישעיהו - תשמור חזק</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411168&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>ישעיהו - תשמור חזק</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>יוסף חיים - איש שחולם געגוע</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411167&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>יוסף חיים - איש שחולם געגוע</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>יהונתן ישראל - רק לעלות</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411166&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>יהונתן ישראל - רק לעלות</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>חן כהן - תל גיבורים</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411165&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>חן כהן - תל גיבורים</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>הייפ קרו - אהבה עיוורת</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411164&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>הייפ קרו - אהבה עיוורת</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>אלינור חלילוב - מחרוזת קיץ 2026</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411163&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>אלינור חלילוב - מחרוזת קיץ 2026</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>אברהם חתומה - כשהלב בקרשים</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411162&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>אברהם חתומה - כשהלב בקרשים</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>אביאלי חדד - וויסקי בלילות</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411161&amp;sid=13e1d521681219f1f5cc74f85473f139</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-06-02</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>אביאלי חדד - וויסקי בלילות</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L20"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>משינה – כמעט וכאילו</v>
+        <v>מירי מסיקה - לב לבן קאבר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-03</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%a9%d7%99%d7%a0%d7%94-%d7%9b%d7%9e%d7%a2%d7%98-%d7%95%d7%9b%d7%90%d7%99%d7%9c%d7%95/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411187&amp;sid=8c32dea66695624c346eddfe12cc9153</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-03</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"כמעט כאילו" של משינה  מגיע אחרי יותר מארבעה עשורים של יצירה. במקום להציג הצהרה חגיגית או נוסטלגית על 40 שנות קריירה, משינה בוחרת לכתוב שיר על בלבול, ספק, מציאות מתעתעת וחוסר יכולת להכריע. במובן הזה, הוא נשמע מאוד עכשווי למרות</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>משינה – כמעט וכאילו</v>
+        <v>מירי מסיקה - לב לבן קאבר</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אמיר אליהו - כסף הכסף קאבר</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411182&amp;sid=8c32dea66695624c346eddfe12cc9153</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-03</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אמיר אליהו - כסף הכסף קאבר</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מירי מסיקה - לב לבן קאבר</v>
+        <v>ליעד מאיר ואופק אדנק – יוצאת מן הכלל</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411187&amp;sid=8c32dea66695624c346eddfe12cc9153</v>
+        <v>https://yosmusic.com/%d7%9c%d7%99%d7%a2%d7%93-%d7%9e%d7%90%d7%99%d7%a8-%d7%95%d7%90%d7%95%d7%a4%d7%a7-%d7%90%d7%93%d7%a0%d7%a7-%d7%99%d7%95%d7%a6%d7%90%d7%aa-%d7%9e%d7%9f-%d7%94%d7%9b%d7%9c%d7%9c/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>"יוצאת מן הכלל" של ליעד מאיר ואופק אדנק הוא שיר שממוקם היטב בתוך גל הפופ-הים תיכוני הצעיר של השנים האחרונות, כזה שמשלב דאנסהול, רגאטון, ראפ ופופ רומנטי קליל. הוא לא מנסה להיות שיר עמוק או מורכב במיוחד; המטרה שלו היא</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,27 +469,27 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מירי מסיקה - לב לבן קאבר</v>
+        <v>ליעד מאיר ואופק אדנק – יוצאת מן הכלל</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אמיר אליהו - כסף הכסף קאבר</v>
+        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן – וויסקי</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411182&amp;sid=8c32dea66695624c346eddfe12cc9153</v>
+        <v>https://yosmusic.com/%d7%94%d7%9e%d7%a9%d7%a7%d7%a4%d7%99%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a0%d7%95%d7%99%d7%a4%d7%9c%d7%93-%d7%a2%d7%9d-%d7%90%d7%95%d7%a8-%d7%a2%d7%9e%d7%a8%d7%9e%d7%99-%d7%91%d7%a8%d7%95%d7%a7%d7%9e%d7%9f/</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-03</v>
+        <v>2026-06-04</v>
       </c>
       <c r="E3" t="str">
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>"וויסקי" ששר אור עמרמי ברוקמן, ממחיש את אחד מסימני ההיכר של שמוליק נויפלד כמלחין: היכולת לקחת טקסט פשוט יחסית, יומיומי כמעט, ולהעניק לו ממד רגשי רחב באמצעות לחן שנע בין עצב לתקווה. במסגרת הפרויקט "המשקפיים של שמוליק נויפלד". הטקסט מתאר</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -507,12 +507,50 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אמיר אליהו - כסף הכסף קאבר</v>
+        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן – וויסקי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>רוני ידידיה ולירון עמרם – ערב חצוי</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C4" t="str">
+        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a0%d7%99-%d7%99%d7%93%d7%99%d7%93%d7%99%d7%94-%d7%95%d7%9c%d7%99%d7%a8%d7%95%d7%9f-%d7%a2%d7%9e%d7%a8%d7%9d-%d7%a2%d7%a8%d7%91-%d7%97%d7%a6%d7%95%d7%99/</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v>"ערב חצוי" הוא אחד מאותם שירים שלא מבקשים לספר סיפור אלא ליצור מצב תודעתי. הוא פועל פחות כמו שיר עלילה ויותר כמו חלום עירוני, רצף של תמונות, חזיונות ואסוציאציות. הבחירה של רוני ידידיה להלחין דווקא טקסט של תרצה אתר אחרי</v>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>רוני ידידיה ולירון עמרם – ערב חצוי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ליעד מאיר ואופק אדנק – יוצאת מן הכלל</v>
+        <v>בן ארצי – אינטימיות בזמן כאוטי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9c%d7%99%d7%a2%d7%93-%d7%9e%d7%90%d7%99%d7%a8-%d7%95%d7%90%d7%95%d7%a4%d7%a7-%d7%90%d7%93%d7%a0%d7%a7-%d7%99%d7%95%d7%a6%d7%90%d7%aa-%d7%9e%d7%9f-%d7%94%d7%9b%d7%9c%d7%9c/</v>
+        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%90%d7%99%d7%a0%d7%98%d7%99%d7%9e%d7%99%d7%95%d7%aa-%d7%91%d7%96%d7%9e%d7%9f-%d7%9b%d7%90%d7%95%d7%98%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-04</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"יוצאת מן הכלל" של ליעד מאיר ואופק אדנק הוא שיר שממוקם היטב בתוך גל הפופ-הים תיכוני הצעיר של השנים האחרונות, כזה שמשלב דאנסהול, רגאטון, ראפ ופופ רומנטי קליל. הוא לא מנסה להיות שיר עמוק או מורכב במיוחד; המטרה שלו היא</v>
+        <v>"אינטימיות בזמן כאוטי" של בן ארצי מדבר על חרדה, בלבול ורעש חיצוני, אבל נשמע כמעט מנחם. הפער הזה בין התוכן לבין המעטפת המוזיקלית הוא כנראה אחד ממקורות הכוח שלו. השיר אינו עוסק באהבה רומנטית דווקא.  "אינטימיות" כאן היא כמעט צורך</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,88 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ליעד מאיר ואופק אדנק – יוצאת מן הכלל</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן – וויסקי</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%94%d7%9e%d7%a9%d7%a7%d7%a4%d7%99%d7%99%d7%9d-%d7%a9%d7%9c-%d7%a0%d7%95%d7%99%d7%a4%d7%9c%d7%93-%d7%a2%d7%9d-%d7%90%d7%95%d7%a8-%d7%a2%d7%9e%d7%a8%d7%9e%d7%99-%d7%91%d7%a8%d7%95%d7%a7%d7%9e%d7%9f/</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v>"וויסקי" ששר אור עמרמי ברוקמן, ממחיש את אחד מסימני ההיכר של שמוליק נויפלד כמלחין: היכולת לקחת טקסט פשוט יחסית, יומיומי כמעט, ולהעניק לו ממד רגשי רחב באמצעות לחן שנע בין עצב לתקווה. במסגרת הפרויקט "המשקפיים של שמוליק נויפלד". הטקסט מתאר</v>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן – וויסקי</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>רוני ידידיה ולירון עמרם – ערב חצוי</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="C4" t="str">
-        <v>https://yosmusic.com/%d7%a8%d7%95%d7%a0%d7%99-%d7%99%d7%93%d7%99%d7%93%d7%99%d7%94-%d7%95%d7%9c%d7%99%d7%a8%d7%95%d7%9f-%d7%a2%d7%9e%d7%a8%d7%9d-%d7%a2%d7%a8%d7%91-%d7%97%d7%a6%d7%95%d7%99/</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-06-04</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v>"ערב חצוי" הוא אחד מאותם שירים שלא מבקשים לספר סיפור אלא ליצור מצב תודעתי. הוא פועל פחות כמו שיר עלילה ויותר כמו חלום עירוני, רצף של תמונות, חזיונות ואסוציאציות. הבחירה של רוני ידידיה להלחין דווקא טקסט של תרצה אתר אחרי</v>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>רוני ידידיה ולירון עמרם – ערב חצוי</v>
+        <v>בן ארצי – אינטימיות בזמן כאוטי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L4"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בן ארצי – אינטימיות בזמן כאוטי</v>
+        <v>שושנה קנו - שופוני</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-04</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%9f-%d7%90%d7%a8%d7%a6%d7%99-%d7%90%d7%99%d7%a0%d7%98%d7%99%d7%9e%d7%99%d7%95%d7%aa-%d7%91%d7%96%d7%9e%d7%9f-%d7%9b%d7%90%d7%95%d7%98%d7%99/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411211&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-04</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"אינטימיות בזמן כאוטי" של בן ארצי מדבר על חרדה, בלבול ורעש חיצוני, אבל נשמע כמעט מנחם. הפער הזה בין התוכן לבין המעטפת המוזיקלית הוא כנראה אחד ממקורות הכוח שלו. השיר אינו עוסק באהבה רומנטית דווקא.  "אינטימיות" כאן היא כמעט צורך</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בן ארצי – אינטימיות בזמן כאוטי</v>
+        <v>שושנה קנו - שופוני</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>רוני ידידיה מארח את לירון עמרם - ערב חצוי</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411210&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>רוני ידידיה מארח את לירון עמרם - ערב חצוי</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>נוי מיהלי - רק תקופה</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411209&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>נוי מיהלי - רק תקופה</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>מתן חסן - בחורה לחתונה</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411208&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>מתן חסן - בחורה לחתונה</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ליעד מאיר &amp; אופק אדנק - יוצאת מן הכלל</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411207&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ליעד מאיר &amp; אופק אדנק - יוצאת מן הכלל</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>לינור דהן - רצוא ושוב</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411206&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>לינור דהן - רצוא ושוב</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ליאור ברגר - כשאת לידי</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411205&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ליאור ברגר - כשאת לידי</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>ידידיה חייט - עמוק בתוך הלב</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411204&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>ידידיה חייט - עמוק בתוך הלב</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>גל ג'ומה - הילטון</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411203&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>גל ג'ומה - הילטון</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אליעד מלכי - שקיעות</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411202&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אליעד מלכי - שקיעות</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>אבישי עוזיאל - תרקדי איתי עכשיו</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="C12" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411201&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-06-04</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v/>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>אבישי עוזיאל - תרקדי איתי עכשיו</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:L26"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שושנה קנו - שופוני</v>
+        <v>שיר זוארץ - שיר של אהבה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411211&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411237&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שושנה קנו - שופוני</v>
+        <v>שיר זוארץ - שיר של אהבה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>רוני ידידיה מארח את לירון עמרם - ערב חצוי</v>
+        <v>רמי מור - זה נגמר</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411210&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411236&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>רוני ידידיה מארח את לירון עמרם - ערב חצוי</v>
+        <v>רמי מור - זה נגמר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>נוי מיהלי - רק תקופה</v>
+        <v>רונה גולד - רוקדת</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411209&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411235&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>נוי מיהלי - רק תקופה</v>
+        <v>רונה גולד - רוקדת</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>מתן חסן - בחורה לחתונה</v>
+        <v>עידו כנפי - רק הזיכרון</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411208&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411234&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>מתן חסן - בחורה לחתונה</v>
+        <v>עידו כנפי - רק הזיכרון</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ליעד מאיר &amp; אופק אדנק - יוצאת מן הכלל</v>
+        <v>משה קליין - כל הטוב</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411207&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411233&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ליעד מאיר &amp; אופק אדנק - יוצאת מן הכלל</v>
+        <v>משה קליין - כל הטוב</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>לינור דהן - רצוא ושוב</v>
+        <v>ירון בר - ודע שלעתיד</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411206&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411232&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>לינור דהן - רצוא ושוב</v>
+        <v>ירון בר - ודע שלעתיד</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ליאור ברגר - כשאת לידי</v>
+        <v>זוהר חודדי - תמיד שמח קאבר</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411205&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411231&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ליאור ברגר - כשאת לידי</v>
+        <v>זוהר חודדי - תמיד שמח קאבר</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>ידידיה חייט - עמוק בתוך הלב</v>
+        <v>התחנה האחרונה - המנון גביע שווגר</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411204&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411230&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>ידידיה חייט - עמוק בתוך הלב</v>
+        <v>התחנה האחרונה - המנון גביע שווגר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>גל ג'ומה - הילטון</v>
+        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן - וויסקי</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411203&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411229&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>גל ג'ומה - הילטון</v>
+        <v>המשקפיים של נויפלד עם אור עמרמי ברוקמן - וויסקי</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אליעד מלכי - שקיעות</v>
+        <v>דניאל אביב - לאיבוד</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411202&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411228&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,21 +811,21 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אליעד מלכי - שקיעות</v>
+        <v>דניאל אביב - לאיבוד</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>אבישי עוזיאל - תרקדי איתי עכשיו</v>
+        <v>אורי זר - את באה ונגעת</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="C12" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411201&amp;sid=9d1ee758a3279cefa6c1a14389a2b3fd</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411227&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-06-04</v>
+        <v>2026-06-05</v>
       </c>
       <c r="E12" t="str">
         <v/>
@@ -849,12 +849,544 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>אבישי עוזיאל - תרקדי איתי עכשיו</v>
+        <v>אורי זר - את באה ונגעת</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>אדיר ניזרי - מחרוזת זה הרגע 2026</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C13" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411226&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D13" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E13" t="str">
+        <v/>
+      </c>
+      <c r="F13" t="str">
+        <v/>
+      </c>
+      <c r="G13" t="str">
+        <v/>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+      <c r="I13" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J13" t="str">
+        <v/>
+      </c>
+      <c r="K13" t="str">
+        <v/>
+      </c>
+      <c r="L13" t="str">
+        <v>אדיר ניזרי - מחרוזת זה הרגע 2026</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>אדיר ניזרי - מחרוזת בית״ר הדגל של המדינה 2026</v>
+      </c>
+      <c r="B14" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C14" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411225&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D14" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E14" t="str">
+        <v/>
+      </c>
+      <c r="F14" t="str">
+        <v/>
+      </c>
+      <c r="G14" t="str">
+        <v/>
+      </c>
+      <c r="H14" t="str">
+        <v/>
+      </c>
+      <c r="I14" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J14" t="str">
+        <v/>
+      </c>
+      <c r="K14" t="str">
+        <v/>
+      </c>
+      <c r="L14" t="str">
+        <v>אדיר ניזרי - מחרוזת בית״ר הדגל של המדינה 2026</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>אדיר ניזרי - מחרוזת אני אוהב אותך בית״ר 2026</v>
+      </c>
+      <c r="B15" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C15" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411224&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D15" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E15" t="str">
+        <v/>
+      </c>
+      <c r="F15" t="str">
+        <v/>
+      </c>
+      <c r="G15" t="str">
+        <v/>
+      </c>
+      <c r="H15" t="str">
+        <v/>
+      </c>
+      <c r="I15" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J15" t="str">
+        <v/>
+      </c>
+      <c r="K15" t="str">
+        <v/>
+      </c>
+      <c r="L15" t="str">
+        <v>אדיר ניזרי - מחרוזת אני אוהב אותך בית״ר 2026</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>מור זיתוני - באתי הביתה</v>
+      </c>
+      <c r="B16" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C16" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411223&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D16" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E16" t="str">
+        <v/>
+      </c>
+      <c r="F16" t="str">
+        <v/>
+      </c>
+      <c r="G16" t="str">
+        <v/>
+      </c>
+      <c r="H16" t="str">
+        <v/>
+      </c>
+      <c r="I16" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J16" t="str">
+        <v/>
+      </c>
+      <c r="K16" t="str">
+        <v/>
+      </c>
+      <c r="L16" t="str">
+        <v>מור זיתוני - באתי הביתה</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="str">
+        <v>מאור בן חיים - סימן קטן</v>
+      </c>
+      <c r="B17" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C17" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411222&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D17" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E17" t="str">
+        <v/>
+      </c>
+      <c r="F17" t="str">
+        <v/>
+      </c>
+      <c r="G17" t="str">
+        <v/>
+      </c>
+      <c r="H17" t="str">
+        <v/>
+      </c>
+      <c r="I17" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J17" t="str">
+        <v/>
+      </c>
+      <c r="K17" t="str">
+        <v/>
+      </c>
+      <c r="L17" t="str">
+        <v>מאור בן חיים - סימן קטן</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>ליאל אברהם - שנינו כאן</v>
+      </c>
+      <c r="B18" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C18" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411221&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D18" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E18" t="str">
+        <v/>
+      </c>
+      <c r="F18" t="str">
+        <v/>
+      </c>
+      <c r="G18" t="str">
+        <v/>
+      </c>
+      <c r="H18" t="str">
+        <v/>
+      </c>
+      <c r="I18" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J18" t="str">
+        <v/>
+      </c>
+      <c r="K18" t="str">
+        <v/>
+      </c>
+      <c r="L18" t="str">
+        <v>ליאל אברהם - שנינו כאן</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>ינון טייב - ויהי בנסוע הארון</v>
+      </c>
+      <c r="B19" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C19" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411220&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D19" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E19" t="str">
+        <v/>
+      </c>
+      <c r="F19" t="str">
+        <v/>
+      </c>
+      <c r="G19" t="str">
+        <v/>
+      </c>
+      <c r="H19" t="str">
+        <v/>
+      </c>
+      <c r="I19" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J19" t="str">
+        <v/>
+      </c>
+      <c r="K19" t="str">
+        <v/>
+      </c>
+      <c r="L19" t="str">
+        <v>ינון טייב - ויהי בנסוע הארון</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>יוני גרייב - אם את עוד אוהבת</v>
+      </c>
+      <c r="B20" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C20" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411219&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D20" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E20" t="str">
+        <v/>
+      </c>
+      <c r="F20" t="str">
+        <v/>
+      </c>
+      <c r="G20" t="str">
+        <v/>
+      </c>
+      <c r="H20" t="str">
+        <v/>
+      </c>
+      <c r="I20" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J20" t="str">
+        <v/>
+      </c>
+      <c r="K20" t="str">
+        <v/>
+      </c>
+      <c r="L20" t="str">
+        <v>יוני גרייב - אם את עוד אוהבת</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>דורון הברי - התיקון שלך</v>
+      </c>
+      <c r="B21" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C21" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411218&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D21" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E21" t="str">
+        <v/>
+      </c>
+      <c r="F21" t="str">
+        <v/>
+      </c>
+      <c r="G21" t="str">
+        <v/>
+      </c>
+      <c r="H21" t="str">
+        <v/>
+      </c>
+      <c r="I21" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J21" t="str">
+        <v/>
+      </c>
+      <c r="K21" t="str">
+        <v/>
+      </c>
+      <c r="L21" t="str">
+        <v>דורון הברי - התיקון שלך</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>דולב שמחי - השם שלך</v>
+      </c>
+      <c r="B22" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C22" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411217&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D22" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E22" t="str">
+        <v/>
+      </c>
+      <c r="F22" t="str">
+        <v/>
+      </c>
+      <c r="G22" t="str">
+        <v/>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v/>
+      </c>
+      <c r="L22" t="str">
+        <v>דולב שמחי - השם שלך</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="str">
+        <v>בן עשור - הרי את מקודשת</v>
+      </c>
+      <c r="B23" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C23" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411216&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D23" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E23" t="str">
+        <v/>
+      </c>
+      <c r="F23" t="str">
+        <v/>
+      </c>
+      <c r="G23" t="str">
+        <v/>
+      </c>
+      <c r="H23" t="str">
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
+      </c>
+      <c r="L23" t="str">
+        <v>בן עשור - הרי את מקודשת</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="str">
+        <v>בן מצמבר - עד מתי</v>
+      </c>
+      <c r="B24" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C24" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411215&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D24" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E24" t="str">
+        <v/>
+      </c>
+      <c r="F24" t="str">
+        <v/>
+      </c>
+      <c r="G24" t="str">
+        <v/>
+      </c>
+      <c r="H24" t="str">
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
+      </c>
+      <c r="L24" t="str">
+        <v>בן מצמבר - עד מתי</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v>ארי בן מתתיהו שלי - ירושלים בליבי</v>
+      </c>
+      <c r="B25" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C25" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411214&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D25" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E25" t="str">
+        <v/>
+      </c>
+      <c r="F25" t="str">
+        <v/>
+      </c>
+      <c r="G25" t="str">
+        <v/>
+      </c>
+      <c r="H25" t="str">
+        <v/>
+      </c>
+      <c r="I25" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J25" t="str">
+        <v/>
+      </c>
+      <c r="K25" t="str">
+        <v/>
+      </c>
+      <c r="L25" t="str">
+        <v>ארי בן מתתיהו שלי - ירושלים בליבי</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>אורין צדקיהו - בייבי</v>
+      </c>
+      <c r="B26" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="C26" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411213&amp;sid=44f7c16fc6a9b4776fe748c4e6b7f986</v>
+      </c>
+      <c r="D26" t="str">
+        <v>2026-06-05</v>
+      </c>
+      <c r="E26" t="str">
+        <v/>
+      </c>
+      <c r="F26" t="str">
+        <v/>
+      </c>
+      <c r="G26" t="str">
+        <v/>
+      </c>
+      <c r="H26" t="str">
+        <v/>
+      </c>
+      <c r="I26" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J26" t="str">
+        <v/>
+      </c>
+      <c r="K26" t="str">
+        <v/>
+      </c>
+      <c r="L26" t="str">
+        <v>אורין צדקיהו - בייבי</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L26"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L3"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>פרויקט אסי עזר – כל מה שעוזר</v>
+        <v>אדיר ניזרי - מחרוזת החשמל חוזר אל הבירה 2026</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-06</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%90%d7%a1%d7%99-%d7%a2%d7%96%d7%a8-%d7%9b%d7%9c-%d7%9e%d7%94-%d7%a9%d7%a2%d7%95%d7%96%d7%a8/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411241&amp;sid=83040952a8788a385111ace586a8d065</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-06</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>פרויקט "כל מה שעוזר" של אסי עזר, בשיתוף אבי אוחיון ומתן דרור, הוא דוגמה מעניינת לאופן שבו תרבות פופולרית יכולה לשמש כלי חברתי, חינוכי ורגשי גם יחד. מדובר לא רק בפרויקט מוזיקלי, אלא במיזם אודיו־ויזואלי בעל מטרה מוצהרת: להפוך את</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,50 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>פרויקט אסי עזר – כל מה שעוזר</v>
+        <v>אדיר ניזרי - מחרוזת החשמל חוזר אל הבירה 2026</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>אליאור נונה - מחרוזת הראש נדלק 2026</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411240&amp;sid=83040952a8788a385111ace586a8d065</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-06</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>אליאור נונה - מחרוזת הראש נדלק 2026</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L3"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אדיר ניזרי - מחרוזת החשמל חוזר אל הבירה 2026</v>
+        <v>דיסקו שמש – ימינושמאל</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411241&amp;sid=83040952a8788a385111ace586a8d065</v>
+        <v>https://yosmusic.com/%d7%93%d7%99%d7%a1%d7%a7%d7%95-%d7%a9%d7%9e%d7%a9-%d7%99%d7%9e%d7%99%d7%a0%d7%95%d7%a9%d7%9e%d7%90%d7%9c/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-06-06</v>
+        <v>2026-06-07</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>השיר "ימינושמאל" של ההרכב "דיסקו שמש" (בשיתוף שי להב וצביקה כהן) מבצע פעולה מרתקת של פירוק והרכבה מחדש (דה-קונסטרוקציה) לקלאסיקה הציונית "אורחה במדבר" (יעקב פיכמן / דוד זהבי). בעוד השיר המקורי, המוכר בין היתר בביצועה המלנכולי-רומנטי של אסתר עופרים, מתאר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,50 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אדיר ניזרי - מחרוזת החשמל חוזר אל הבירה 2026</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>אליאור נונה - מחרוזת הראש נדלק 2026</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411240&amp;sid=83040952a8788a385111ace586a8d065</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-06-06</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>אליאור נונה - מחרוזת הראש נדלק 2026</v>
+        <v>דיסקו שמש – ימינושמאל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L9"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>דיסקו שמש – ימינושמאל</v>
+        <v>להקת דרך - זה הזמן</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%93%d7%99%d7%a1%d7%a7%d7%95-%d7%a9%d7%9e%d7%a9-%d7%99%d7%9e%d7%99%d7%a0%d7%95%d7%a9%d7%9e%d7%90%d7%9c/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411256&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-07</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "ימינושמאל" של ההרכב "דיסקו שמש" (בשיתוף שי להב וצביקה כהן) מבצע פעולה מרתקת של פירוק והרכבה מחדש (דה-קונסטרוקציה) לקלאסיקה הציונית "אורחה במדבר" (יעקב פיכמן / דוד זהבי). בעוד השיר המקורי, המוכר בין היתר בביצועה המלנכולי-רומנטי של אסתר עופרים, מתאר</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,278 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>דיסקו שמש – ימינושמאל</v>
+        <v>להקת דרך - זה הזמן</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>חגית ביטון חג'בי - An Optimic Day</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411255&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>חגית ביטון חג'בי - An Optimic Day</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>הדר אבני - בואי</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411254&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>הדר אבני - בואי</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>גיל ישראלוב &amp; שימי יונייב ותזמורתו - מחרוזת יאסו טאנץ 2026</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411253&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>גיל ישראלוב &amp; שימי יונייב ותזמורתו - מחרוזת יאסו טאנץ 2026</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>ג'ולי עידן - פרידה</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411252&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>ג'ולי עידן - פרידה</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>בן ארצי - אינטימיות בזמן כאוטי</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411251&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>בן ארצי - אינטימיות בזמן כאוטי</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>אלקנה אלפסי - מחפש משמעות</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411250&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>אלקנה אלפסי - מחפש משמעות</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אלעד אלדד - תגיד תודה</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411249&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-06-07</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אלעד אלדד - תגיד תודה</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L9"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-06-week01/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>להקת דרך - זה הזמן</v>
+        <v>שיראל חדד - קנאה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411256&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411264&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D2" t="str">
         <v>2026-06-07</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>להקת דרך - זה הזמן</v>
+        <v>שיראל חדד - קנאה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>חגית ביטון חג'בי - An Optimic Day</v>
+        <v>רון שובל - תחת החופה</v>
       </c>
       <c r="B3" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411255&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411263&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D3" t="str">
         <v>2026-06-07</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>חגית ביטון חג'בי - An Optimic Day</v>
+        <v>רון שובל - תחת החופה</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>הדר אבני - בואי</v>
+        <v>רון חיון - גבר מרוקאי</v>
       </c>
       <c r="B4" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411254&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411262&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D4" t="str">
         <v>2026-06-07</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>הדר אבני - בואי</v>
+        <v>רון חיון - גבר מרוקאי</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>גיל ישראלוב &amp; שימי יונייב ותזמורתו - מחרוזת יאסו טאנץ 2026</v>
+        <v>עמית אבני &amp; מאור כהן - עשרים וארבע</v>
       </c>
       <c r="B5" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411253&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411261&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D5" t="str">
         <v>2026-06-07</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>גיל ישראלוב &amp; שימי יונייב ותזמורתו - מחרוזת יאסו טאנץ 2026</v>
+        <v>עמית אבני &amp; מאור כהן - עשרים וארבע</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>ג'ולי עידן - פרידה</v>
+        <v>סדריק מארח את אפק לאמור - רק רוצה לחיות פה</v>
       </c>
       <c r="B6" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411252&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411260&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D6" t="str">
         <v>2026-06-07</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>ג'ולי עידן - פרידה</v>
+        <v>סדריק מארח את אפק לאמור - רק רוצה לחיות פה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>בן ארצי - אינטימיות בזמן כאוטי</v>
+        <v>נתנאל מלכה - מי יחבק אותך</v>
       </c>
       <c r="B7" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411251&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411259&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D7" t="str">
         <v>2026-06-07</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>בן ארצי - אינטימיות בזמן כאוטי</v>
+        <v>נתנאל מלכה - מי יחבק אותך</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אלקנה אלפסי - מחפש משמעות</v>
+        <v>נשמה וקצב - בלעדיה</v>
       </c>
       <c r="B8" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411250&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411258&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D8" t="str">
         <v>2026-06-07</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אלקנה אלפסי - מחפש משמעות</v>
+        <v>נשמה וקצב - בלעדיה</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אלעד אלדד - תגיד תודה</v>
+        <v>ניסים ברנס - הולך על בטוח</v>
       </c>
       <c r="B9" t="str">
         <v>2026-06-07</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411249&amp;sid=bc152818ce4bc6ae728a7cfe19a9afe2</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411257&amp;sid=261e1664a9c51f5f15b138b08253c90e</v>
       </c>
       <c r="D9" t="str">
         <v>2026-06-07</v>
@@ -735,7 +735,7 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אלעד אלדד - תגיד תודה</v>
+        <v>ניסים ברנס - הולך על בטוח</v>
       </c>
     </row>
   </sheetData>
